--- a/tools/catalogue.xlsx
+++ b/tools/catalogue.xlsx
@@ -1,31 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\tax docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AbtaalAatif\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC328F5-F27E-4691-88E8-70BD124A8D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF28982-2262-4673-85C5-30389ADD6AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="162">
   <si>
     <t>Collection</t>
   </si>
@@ -240,9 +235,6 @@
     <t>Sea Salt</t>
   </si>
   <si>
-    <t>Raw Almond Flour (1kg)</t>
-  </si>
-  <si>
     <t>Blanched Almond Flour (super fine imported) (1kg)</t>
   </si>
   <si>
@@ -463,9 +455,6 @@
   </si>
   <si>
     <t>Unrefined, unprocessed sea salt with coarse texture; no additives; rich in minerals; macros not provided.</t>
-  </si>
-  <si>
-    <t>Premium raw almond flour made from freshly roasted American almonds; gluten-free and keto-friendly; macros not provided.</t>
   </si>
   <si>
     <t>Super fine blanched almond flour imported from renowned mills; perfect for baking; macros not provided.</t>
@@ -575,12 +564,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -600,9 +588,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -640,9 +628,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -675,26 +663,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -727,26 +698,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -920,14 +874,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D78"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D77"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="59.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="59.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -941,441 +895,441 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>2200</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>2700</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>2500</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>1350</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6">
         <v>650</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>2800</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>4</v>
       </c>
       <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>5600</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>4</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>3300</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>4</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>5200</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>4</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <v>2200</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>4</v>
       </c>
       <c r="B12" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <v>1900</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>4</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <v>5200</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>4</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <v>1600</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>4</v>
       </c>
       <c r="B15" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="2">
         <v>4900</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>4</v>
       </c>
       <c r="B16" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <v>5200</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>4</v>
       </c>
       <c r="B17" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17">
         <v>850</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>4</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <v>1440</v>
       </c>
       <c r="D18" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>4</v>
       </c>
       <c r="B19" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <v>4600</v>
       </c>
       <c r="D19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>4</v>
       </c>
       <c r="B20" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="2">
         <v>2500</v>
       </c>
       <c r="D20" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>4</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="2">
         <v>1900</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>4</v>
       </c>
       <c r="B22" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="2">
         <v>2000</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>4</v>
       </c>
       <c r="B23" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="2">
         <v>3500</v>
       </c>
       <c r="D23" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>4</v>
       </c>
       <c r="B24" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24">
         <v>450</v>
       </c>
       <c r="D24" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>4</v>
       </c>
       <c r="B25" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25">
         <v>550</v>
       </c>
       <c r="D25" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>4</v>
       </c>
       <c r="B26" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="2">
         <v>2700</v>
       </c>
       <c r="D26" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>5</v>
       </c>
       <c r="B27" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27">
         <v>950</v>
       </c>
       <c r="D27" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>5</v>
       </c>
       <c r="B28" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="2">
         <v>1950</v>
       </c>
       <c r="D28" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>5</v>
       </c>
       <c r="B29" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29">
         <v>600</v>
       </c>
       <c r="D29" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>5</v>
       </c>
       <c r="B30" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30">
         <v>900</v>
       </c>
       <c r="D30" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>5</v>
       </c>
       <c r="B31" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31">
         <v>600</v>
       </c>
       <c r="D31" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>5</v>
       </c>
       <c r="B32" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="2">
         <v>1150</v>
       </c>
       <c r="D32" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -1386,10 +1340,10 @@
         <v>2100</v>
       </c>
       <c r="D33" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -1400,10 +1354,10 @@
         <v>1950</v>
       </c>
       <c r="D34" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -1414,10 +1368,10 @@
         <v>1950</v>
       </c>
       <c r="D35" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -1428,108 +1382,108 @@
         <v>900</v>
       </c>
       <c r="D36" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>6</v>
       </c>
       <c r="B37" t="s">
         <v>50</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="2">
         <v>3000</v>
       </c>
       <c r="D37" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>6</v>
       </c>
       <c r="B38" t="s">
         <v>51</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="2">
         <v>1950</v>
       </c>
       <c r="D38" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>6</v>
       </c>
       <c r="B39" t="s">
         <v>52</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="2">
         <v>2600</v>
       </c>
       <c r="D39" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>6</v>
       </c>
       <c r="B40" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="2">
         <v>1950</v>
       </c>
       <c r="D40" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>6</v>
       </c>
       <c r="B41" t="s">
         <v>54</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="2">
         <v>3000</v>
       </c>
       <c r="D41" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>6</v>
       </c>
       <c r="B42" t="s">
         <v>55</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="2">
         <v>2700</v>
       </c>
       <c r="D42" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>6</v>
       </c>
       <c r="B43" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="2">
         <v>1440</v>
       </c>
       <c r="D43" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>7</v>
       </c>
@@ -1540,10 +1494,10 @@
         <v>1600</v>
       </c>
       <c r="D44" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>7</v>
       </c>
@@ -1554,10 +1508,10 @@
         <v>1900</v>
       </c>
       <c r="D45" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -1568,10 +1522,10 @@
         <v>1900</v>
       </c>
       <c r="D46" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -1582,10 +1536,10 @@
         <v>1700</v>
       </c>
       <c r="D47" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -1596,10 +1550,10 @@
         <v>700</v>
       </c>
       <c r="D48" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>7</v>
       </c>
@@ -1610,10 +1564,10 @@
         <v>1600</v>
       </c>
       <c r="D49" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -1624,10 +1578,10 @@
         <v>2500</v>
       </c>
       <c r="D50" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -1638,10 +1592,10 @@
         <v>1100</v>
       </c>
       <c r="D51" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -1652,10 +1606,10 @@
         <v>2800</v>
       </c>
       <c r="D52" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>7</v>
       </c>
@@ -1666,10 +1620,10 @@
         <v>2200</v>
       </c>
       <c r="D53" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>8</v>
       </c>
@@ -1680,10 +1634,10 @@
         <v>3100</v>
       </c>
       <c r="D54" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>9</v>
       </c>
@@ -1694,10 +1648,10 @@
         <v>2100</v>
       </c>
       <c r="D55" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -1708,10 +1662,10 @@
         <v>5250</v>
       </c>
       <c r="D56" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>9</v>
       </c>
@@ -1722,10 +1676,10 @@
         <v>3250</v>
       </c>
       <c r="D57" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>9</v>
       </c>
@@ -1736,10 +1690,10 @@
         <v>2100</v>
       </c>
       <c r="D58" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>10</v>
       </c>
@@ -1750,10 +1704,10 @@
         <v>1600</v>
       </c>
       <c r="D59" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>10</v>
       </c>
@@ -1764,10 +1718,10 @@
         <v>999</v>
       </c>
       <c r="D60" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>10</v>
       </c>
@@ -1775,13 +1729,13 @@
         <v>71</v>
       </c>
       <c r="C61">
-        <v>4500</v>
+        <v>7200</v>
       </c>
       <c r="D61" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>10</v>
       </c>
@@ -1789,13 +1743,13 @@
         <v>72</v>
       </c>
       <c r="C62">
-        <v>7200</v>
+        <v>4000</v>
       </c>
       <c r="D62" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>10</v>
       </c>
@@ -1803,13 +1757,13 @@
         <v>73</v>
       </c>
       <c r="C63">
-        <v>4000</v>
+        <v>2300</v>
       </c>
       <c r="D63" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>10</v>
       </c>
@@ -1817,27 +1771,27 @@
         <v>74</v>
       </c>
       <c r="C64">
-        <v>2300</v>
+        <v>1250</v>
       </c>
       <c r="D64" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B65" t="s">
         <v>75</v>
       </c>
       <c r="C65">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="D65" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>11</v>
       </c>
@@ -1845,13 +1799,13 @@
         <v>76</v>
       </c>
       <c r="C66">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="D66" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>11</v>
       </c>
@@ -1859,41 +1813,41 @@
         <v>77</v>
       </c>
       <c r="C67">
-        <v>1400</v>
+        <v>2650</v>
       </c>
       <c r="D67" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="C68">
-        <v>2650</v>
+        <v>2100</v>
       </c>
       <c r="D68" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="C69">
-        <v>2100</v>
+        <v>1300</v>
       </c>
       <c r="D69" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>11</v>
       </c>
@@ -1901,27 +1855,27 @@
         <v>79</v>
       </c>
       <c r="C70">
-        <v>1300</v>
+        <v>2800</v>
       </c>
       <c r="D70" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B71" t="s">
         <v>80</v>
       </c>
       <c r="C71">
-        <v>2800</v>
+        <v>1500</v>
       </c>
       <c r="D71" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>12</v>
       </c>
@@ -1929,27 +1883,27 @@
         <v>81</v>
       </c>
       <c r="C72">
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="D72" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B73" t="s">
         <v>82</v>
       </c>
       <c r="C73">
-        <v>2200</v>
+        <v>175</v>
       </c>
       <c r="D73" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>13</v>
       </c>
@@ -1957,13 +1911,13 @@
         <v>83</v>
       </c>
       <c r="C74">
-        <v>175</v>
+        <v>500</v>
       </c>
       <c r="D74" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>13</v>
       </c>
@@ -1971,27 +1925,27 @@
         <v>84</v>
       </c>
       <c r="C75">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="D75" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B76" t="s">
         <v>85</v>
       </c>
       <c r="C76">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="D76" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>14</v>
       </c>
@@ -1999,24 +1953,10 @@
         <v>86</v>
       </c>
       <c r="C77">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="D77" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>14</v>
-      </c>
-      <c r="B78" t="s">
-        <v>87</v>
-      </c>
-      <c r="C78">
-        <v>950</v>
-      </c>
-      <c r="D78" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/tools/catalogue.xlsx
+++ b/tools/catalogue.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AbtaalAatif\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\tax docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF28982-2262-4673-85C5-30389ADD6AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC328F5-F27E-4691-88E8-70BD124A8D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="164">
   <si>
     <t>Collection</t>
   </si>
@@ -235,6 +240,9 @@
     <t>Sea Salt</t>
   </si>
   <si>
+    <t>Raw Almond Flour (1kg)</t>
+  </si>
+  <si>
     <t>Blanched Almond Flour (super fine imported) (1kg)</t>
   </si>
   <si>
@@ -455,6 +463,9 @@
   </si>
   <si>
     <t>Unrefined, unprocessed sea salt with coarse texture; no additives; rich in minerals; macros not provided.</t>
+  </si>
+  <si>
+    <t>Premium raw almond flour made from freshly roasted American almonds; gluten-free and keto-friendly; macros not provided.</t>
   </si>
   <si>
     <t>Super fine blanched almond flour imported from renowned mills; perfect for baking; macros not provided.</t>
@@ -564,11 +575,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -588,9 +600,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -628,9 +640,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -663,9 +675,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -698,9 +727,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -874,14 +920,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D77"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D78"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="59.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="59.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -895,441 +941,441 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>2200</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>2700</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>2500</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>1350</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>650</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>2800</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
       <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="3">
         <v>5600</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>3300</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>5200</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>2200</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
       <c r="B12" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>1900</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="3">
         <v>5200</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="3">
         <v>1600</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
       <c r="B15" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="3">
         <v>4900</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
       <c r="B16" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="3">
         <v>5200</v>
       </c>
       <c r="D16" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
       <c r="B17" t="s">
         <v>30</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="2">
         <v>850</v>
       </c>
       <c r="D17" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="3">
         <v>1440</v>
       </c>
       <c r="D18" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
       <c r="B19" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="3">
         <v>4600</v>
       </c>
       <c r="D19" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
       <c r="B20" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="3">
         <v>2500</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="3">
         <v>1900</v>
       </c>
       <c r="D21" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
       <c r="B22" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="3">
         <v>2000</v>
       </c>
       <c r="D22" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
       <c r="B23" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="3">
         <v>3500</v>
       </c>
       <c r="D23" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
       <c r="B24" t="s">
         <v>37</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="2">
         <v>450</v>
       </c>
       <c r="D24" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
       <c r="B25" t="s">
         <v>38</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="2">
         <v>550</v>
       </c>
       <c r="D25" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>
       <c r="B26" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="3">
         <v>2700</v>
       </c>
       <c r="D26" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>5</v>
       </c>
       <c r="B27" t="s">
         <v>40</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="2">
         <v>950</v>
       </c>
       <c r="D27" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>5</v>
       </c>
       <c r="B28" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="3">
         <v>1950</v>
       </c>
       <c r="D28" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>5</v>
       </c>
       <c r="B29" t="s">
         <v>42</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="2">
         <v>600</v>
       </c>
       <c r="D29" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>5</v>
       </c>
       <c r="B30" t="s">
         <v>43</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="2">
         <v>900</v>
       </c>
       <c r="D30" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>5</v>
       </c>
       <c r="B31" t="s">
         <v>44</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="2">
         <v>600</v>
       </c>
       <c r="D31" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>5</v>
       </c>
       <c r="B32" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="3">
         <v>1150</v>
       </c>
       <c r="D32" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -1340,10 +1386,10 @@
         <v>2100</v>
       </c>
       <c r="D33" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -1354,10 +1400,10 @@
         <v>1950</v>
       </c>
       <c r="D34" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -1368,10 +1414,10 @@
         <v>1950</v>
       </c>
       <c r="D35" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -1382,108 +1428,108 @@
         <v>900</v>
       </c>
       <c r="D36" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>6</v>
       </c>
       <c r="B37" t="s">
         <v>50</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="3">
         <v>3000</v>
       </c>
       <c r="D37" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>6</v>
       </c>
       <c r="B38" t="s">
         <v>51</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="3">
         <v>1950</v>
       </c>
       <c r="D38" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>6</v>
       </c>
       <c r="B39" t="s">
         <v>52</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="3">
         <v>2600</v>
       </c>
       <c r="D39" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>6</v>
       </c>
       <c r="B40" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="3">
         <v>1950</v>
       </c>
       <c r="D40" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>6</v>
       </c>
       <c r="B41" t="s">
         <v>54</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="3">
         <v>3000</v>
       </c>
       <c r="D41" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>6</v>
       </c>
       <c r="B42" t="s">
         <v>55</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="3">
         <v>2700</v>
       </c>
       <c r="D42" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>6</v>
       </c>
       <c r="B43" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="3">
         <v>1440</v>
       </c>
       <c r="D43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>7</v>
       </c>
@@ -1494,10 +1540,10 @@
         <v>1600</v>
       </c>
       <c r="D44" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>7</v>
       </c>
@@ -1508,10 +1554,10 @@
         <v>1900</v>
       </c>
       <c r="D45" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -1522,10 +1568,10 @@
         <v>1900</v>
       </c>
       <c r="D46" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -1536,10 +1582,10 @@
         <v>1700</v>
       </c>
       <c r="D47" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -1550,10 +1596,10 @@
         <v>700</v>
       </c>
       <c r="D48" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>7</v>
       </c>
@@ -1564,10 +1610,10 @@
         <v>1600</v>
       </c>
       <c r="D49" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -1578,10 +1624,10 @@
         <v>2500</v>
       </c>
       <c r="D50" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -1592,10 +1638,10 @@
         <v>1100</v>
       </c>
       <c r="D51" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -1606,10 +1652,10 @@
         <v>2800</v>
       </c>
       <c r="D52" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>7</v>
       </c>
@@ -1620,10 +1666,10 @@
         <v>2200</v>
       </c>
       <c r="D53" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>8</v>
       </c>
@@ -1634,10 +1680,10 @@
         <v>3100</v>
       </c>
       <c r="D54" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>9</v>
       </c>
@@ -1648,10 +1694,10 @@
         <v>2100</v>
       </c>
       <c r="D55" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -1662,10 +1708,10 @@
         <v>5250</v>
       </c>
       <c r="D56" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>9</v>
       </c>
@@ -1676,10 +1722,10 @@
         <v>3250</v>
       </c>
       <c r="D57" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>9</v>
       </c>
@@ -1690,10 +1736,10 @@
         <v>2100</v>
       </c>
       <c r="D58" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>10</v>
       </c>
@@ -1704,10 +1750,10 @@
         <v>1600</v>
       </c>
       <c r="D59" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>10</v>
       </c>
@@ -1718,10 +1764,10 @@
         <v>999</v>
       </c>
       <c r="D60" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>10</v>
       </c>
@@ -1729,13 +1775,13 @@
         <v>71</v>
       </c>
       <c r="C61">
-        <v>7200</v>
+        <v>4500</v>
       </c>
       <c r="D61" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>10</v>
       </c>
@@ -1743,13 +1789,13 @@
         <v>72</v>
       </c>
       <c r="C62">
-        <v>4000</v>
+        <v>7200</v>
       </c>
       <c r="D62" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>10</v>
       </c>
@@ -1757,13 +1803,13 @@
         <v>73</v>
       </c>
       <c r="C63">
-        <v>2300</v>
+        <v>4000</v>
       </c>
       <c r="D63" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>10</v>
       </c>
@@ -1771,27 +1817,27 @@
         <v>74</v>
       </c>
       <c r="C64">
-        <v>1250</v>
+        <v>2300</v>
       </c>
       <c r="D64" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B65" t="s">
         <v>75</v>
       </c>
       <c r="C65">
-        <v>1500</v>
+        <v>1250</v>
       </c>
       <c r="D65" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>11</v>
       </c>
@@ -1799,13 +1845,13 @@
         <v>76</v>
       </c>
       <c r="C66">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="D66" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>11</v>
       </c>
@@ -1813,41 +1859,41 @@
         <v>77</v>
       </c>
       <c r="C67">
-        <v>2650</v>
+        <v>1400</v>
       </c>
       <c r="D67" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="C68">
-        <v>2100</v>
+        <v>2650</v>
       </c>
       <c r="D68" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="C69">
-        <v>1300</v>
+        <v>2100</v>
       </c>
       <c r="D69" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>11</v>
       </c>
@@ -1855,27 +1901,27 @@
         <v>79</v>
       </c>
       <c r="C70">
-        <v>2800</v>
+        <v>1300</v>
       </c>
       <c r="D70" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B71" t="s">
         <v>80</v>
       </c>
       <c r="C71">
-        <v>1500</v>
+        <v>2800</v>
       </c>
       <c r="D71" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>12</v>
       </c>
@@ -1883,27 +1929,27 @@
         <v>81</v>
       </c>
       <c r="C72">
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="D72" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
         <v>82</v>
       </c>
       <c r="C73">
-        <v>175</v>
+        <v>2200</v>
       </c>
       <c r="D73" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>13</v>
       </c>
@@ -1911,13 +1957,13 @@
         <v>83</v>
       </c>
       <c r="C74">
-        <v>500</v>
+        <v>175</v>
       </c>
       <c r="D74" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>13</v>
       </c>
@@ -1925,27 +1971,27 @@
         <v>84</v>
       </c>
       <c r="C75">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D75" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B76" t="s">
         <v>85</v>
       </c>
       <c r="C76">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="D76" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>14</v>
       </c>
@@ -1953,10 +1999,24 @@
         <v>86</v>
       </c>
       <c r="C77">
+        <v>900</v>
+      </c>
+      <c r="D77" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>14</v>
+      </c>
+      <c r="B78" t="s">
+        <v>87</v>
+      </c>
+      <c r="C78">
         <v>950</v>
       </c>
-      <c r="D77" t="s">
-        <v>161</v>
+      <c r="D78" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
